--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/2461-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/2461-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{40361202-1ADB-4ADE-8A4F-4B5C9BB96284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1720F4C9-7625-42E9-98E2-98FA5A213C17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{60933711-6A19-4386-9412-31A68E7C6A89}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{87FB6EBF-3956-43A4-86EE-A55B65F9A5A1}"/>
   </bookViews>
   <sheets>
     <sheet name="2461-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1532,23 +1532,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{831F3309-6849-4E07-BF1F-C692A4B583F6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35D24B58-4FE8-4657-8BD5-A1F8BDC3D978}">
   <dimension ref="A1:R71"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.77734375" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1576,7 +1576,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1606,7 +1606,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1652,7 +1652,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1702,7 +1702,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2026</v>
       </c>
@@ -1756,7 +1756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1812,7 +1812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1868,7 +1868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="39">
         <v>2025</v>
       </c>
@@ -1922,7 +1922,7 @@
         <v>4.8600000000000003</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>25</v>
       </c>
@@ -1978,7 +1978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>25</v>
       </c>
@@ -2034,7 +2034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
         <v>25</v>
       </c>
@@ -2090,7 +2090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
         <v>25</v>
       </c>
@@ -2146,7 +2146,7 @@
         <v>4.8600000000000003</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
         <v>25</v>
       </c>
@@ -2202,7 +2202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="37">
         <v>2024</v>
       </c>
@@ -2256,7 +2256,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>25</v>
       </c>
@@ -2312,7 +2312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>25</v>
       </c>
@@ -2368,7 +2368,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>25</v>
       </c>
@@ -2424,7 +2424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>25</v>
       </c>
@@ -2480,7 +2480,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
@@ -2536,7 +2536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="39">
         <v>2023</v>
       </c>
@@ -2590,7 +2590,7 @@
         <v>6.12</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>25</v>
       </c>
@@ -2646,7 +2646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>25</v>
       </c>
@@ -2702,7 +2702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
         <v>25</v>
       </c>
@@ -2758,7 +2758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
         <v>25</v>
       </c>
@@ -2814,7 +2814,7 @@
         <v>6.12</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="37">
         <v>2022</v>
       </c>
@@ -2868,7 +2868,7 @@
         <v>7.61</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>25</v>
       </c>
@@ -2924,7 +2924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>25</v>
       </c>
@@ -2980,7 +2980,7 @@
         <v>1.67</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>25</v>
       </c>
@@ -3036,7 +3036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>25</v>
       </c>
@@ -3092,7 +3092,7 @@
         <v>5.94</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="39">
         <v>2021</v>
       </c>
@@ -3146,7 +3146,7 @@
         <v>6.69</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
         <v>25</v>
       </c>
@@ -3202,7 +3202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
         <v>25</v>
       </c>
@@ -3258,7 +3258,7 @@
         <v>2.2599999999999998</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="17" t="s">
         <v>25</v>
       </c>
@@ -3314,7 +3314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="17" t="s">
         <v>25</v>
       </c>
@@ -3370,7 +3370,7 @@
         <v>4.42</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="37">
         <v>2020</v>
       </c>
@@ -3424,7 +3424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
         <v>25</v>
       </c>
@@ -3480,7 +3480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
         <v>25</v>
       </c>
@@ -3536,7 +3536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
         <v>25</v>
       </c>
@@ -3592,7 +3592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
         <v>25</v>
       </c>
@@ -3648,7 +3648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="39">
         <v>2019</v>
       </c>
@@ -3702,7 +3702,7 @@
         <v>2.15</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="17" t="s">
         <v>25</v>
       </c>
@@ -3758,7 +3758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="17" t="s">
         <v>25</v>
       </c>
@@ -3814,7 +3814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="17" t="s">
         <v>25</v>
       </c>
@@ -3870,7 +3870,7 @@
         <v>2.15</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="37">
         <v>2018</v>
       </c>
@@ -3924,7 +3924,7 @@
         <v>3.62</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="39">
         <v>2017</v>
       </c>
@@ -3978,7 +3978,7 @@
         <v>5.24</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="37">
         <v>2016</v>
       </c>
@@ -4032,7 +4032,7 @@
         <v>3.58</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="39">
         <v>2015</v>
       </c>
@@ -4086,7 +4086,7 @@
         <v>2.77</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="37">
         <v>2014</v>
       </c>
@@ -4140,7 +4140,7 @@
         <v>3.79</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="39">
         <v>2013</v>
       </c>
@@ -4194,7 +4194,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="37">
         <v>2012</v>
       </c>
@@ -4248,7 +4248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="39">
         <v>2011</v>
       </c>
@@ -4302,7 +4302,7 @@
         <v>1.59</v>
       </c>
     </row>
-    <row r="52" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="37">
         <v>2010</v>
       </c>
@@ -4356,7 +4356,7 @@
         <v>1.45</v>
       </c>
     </row>
-    <row r="53" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="39">
         <v>2009</v>
       </c>
@@ -4410,7 +4410,7 @@
         <v>1.55</v>
       </c>
     </row>
-    <row r="54" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="37">
         <v>2008</v>
       </c>
@@ -4464,7 +4464,7 @@
         <v>9.58</v>
       </c>
     </row>
-    <row r="55" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="39">
         <v>2007</v>
       </c>
@@ -4518,7 +4518,7 @@
         <v>2.36</v>
       </c>
     </row>
-    <row r="56" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="37">
         <v>2006</v>
       </c>
@@ -4572,7 +4572,7 @@
         <v>2.17</v>
       </c>
     </row>
-    <row r="57" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="39">
         <v>2005</v>
       </c>
@@ -4626,7 +4626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="37">
         <v>2004</v>
       </c>
@@ -4680,7 +4680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="39">
         <v>2003</v>
       </c>
@@ -4734,7 +4734,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="60" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="37">
         <v>2002</v>
       </c>
@@ -4788,7 +4788,7 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="61" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="39">
         <v>2001</v>
       </c>
@@ -4842,7 +4842,7 @@
         <v>5.36</v>
       </c>
     </row>
-    <row r="62" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="37">
         <v>2000</v>
       </c>
@@ -4896,7 +4896,7 @@
         <v>3.01</v>
       </c>
     </row>
-    <row r="63" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A63" s="39">
         <v>1999</v>
       </c>
@@ -4950,7 +4950,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="64" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A64" s="37">
         <v>1998</v>
       </c>
@@ -5004,7 +5004,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="65" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A65" s="39">
         <v>1997</v>
       </c>
@@ -5058,7 +5058,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="66" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A66" s="37">
         <v>1996</v>
       </c>
@@ -5112,7 +5112,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="67" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A67" s="39">
         <v>1995</v>
       </c>
@@ -5166,7 +5166,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="68" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A68" s="37">
         <v>1994</v>
       </c>
@@ -5220,7 +5220,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="69" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A69" s="39">
         <v>1993</v>
       </c>
@@ -5274,7 +5274,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="70" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A70" s="37">
         <v>1991</v>
       </c>
@@ -5328,7 +5328,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="71" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A71" s="39" t="s">
         <v>63</v>
       </c>
